--- a/Team-Data/2008-09/2-11-2008-09.xlsx
+++ b/Team-Data/2008-09/2-11-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.596</v>
+        <v>0.588</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -679,16 +746,16 @@
         <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
         <v>7.8</v>
       </c>
       <c r="M2" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="N2" t="n">
         <v>0.372</v>
@@ -700,25 +767,25 @@
         <v>25.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R2" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S2" t="n">
         <v>29.6</v>
       </c>
       <c r="T2" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U2" t="n">
         <v>21.2</v>
       </c>
       <c r="V2" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W2" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X2" t="n">
         <v>4.6</v>
@@ -727,7 +794,7 @@
         <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA2" t="n">
         <v>20.9</v>
@@ -739,10 +806,10 @@
         <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="n">
         <v>10</v>
@@ -751,37 +818,37 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
         <v>13</v>
       </c>
       <c r="AL2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO2" t="n">
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -790,28 +857,28 @@
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA2" t="n">
         <v>19</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -873,22 +940,22 @@
         <v>16.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.777</v>
+        <v>0.773</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T3" t="n">
         <v>42.8</v>
@@ -909,7 +976,7 @@
         <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
         <v>22.8</v>
@@ -918,19 +985,19 @@
         <v>101.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
         <v>11</v>
@@ -954,28 +1021,28 @@
         <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
@@ -984,7 +1051,7 @@
         <v>13</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>0.404</v>
+        <v>0.392</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="J4" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M4" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O4" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P4" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="R4" t="n">
         <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T4" t="n">
         <v>39</v>
       </c>
       <c r="U4" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
         <v>15.6</v>
@@ -1085,37 +1152,37 @@
         <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y4" t="n">
         <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA4" t="n">
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.2</v>
+        <v>92</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1145,13 +1212,13 @@
         <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
         <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="n">
         <v>14</v>
@@ -1160,10 +1227,10 @@
         <v>26</v>
       </c>
       <c r="AW4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX4" t="n">
         <v>18</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>17</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,13 +1239,13 @@
         <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>0.431</v>
+        <v>0.442</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
@@ -1225,28 +1292,28 @@
         <v>37.8</v>
       </c>
       <c r="J5" t="n">
-        <v>84.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
         <v>0.45</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O5" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="P5" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R5" t="n">
         <v>12.1</v>
@@ -1255,13 +1322,13 @@
         <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
         <v>7.4</v>
@@ -1273,43 +1340,43 @@
         <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.3</v>
+        <v>100.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM5" t="n">
         <v>23</v>
@@ -1318,34 +1385,34 @@
         <v>9</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
         <v>15</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
@@ -1354,13 +1421,13 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -1392,49 +1459,49 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="J6" t="n">
-        <v>78.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.384</v>
+        <v>0.381</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R6" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
         <v>41.8</v>
@@ -1443,73 +1510,73 @@
         <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="W6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.2</v>
+        <v>100.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>25</v>
       </c>
-      <c r="AI6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>20</v>
-      </c>
       <c r="AK6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM6" t="n">
         <v>5</v>
       </c>
-      <c r="AL6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>4</v>
-      </c>
       <c r="AN6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
         <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1518,28 +1585,28 @@
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV6" t="n">
         <v>5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
         <v>4</v>
       </c>
-      <c r="AY6" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
         <v>21</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -1649,34 +1716,34 @@
         <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="n">
         <v>9</v>
       </c>
-      <c r="AF7" t="n">
-        <v>8</v>
-      </c>
       <c r="AG7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ7" t="n">
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
         <v>13</v>
       </c>
       <c r="AM7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN7" t="n">
         <v>24</v>
@@ -1694,13 +1761,13 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT7" t="n">
         <v>5</v>
       </c>
-      <c r="AT7" t="n">
-        <v>4</v>
-      </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
@@ -1709,10 +1776,10 @@
         <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1721,10 +1788,10 @@
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -1753,31 +1820,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
         <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="J8" t="n">
-        <v>78.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
         <v>17.8</v>
@@ -1792,46 +1859,46 @@
         <v>30.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R8" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T8" t="n">
         <v>40.9</v>
       </c>
       <c r="U8" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="V8" t="n">
         <v>15.6</v>
       </c>
       <c r="W8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.5</v>
+        <v>103.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1843,25 +1910,25 @@
         <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
         <v>15</v>
       </c>
       <c r="AM8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN8" t="n">
         <v>17</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>16</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,16 +1940,16 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS8" t="n">
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
         <v>25</v>
@@ -1897,7 +1964,7 @@
         <v>27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -1935,22 +2002,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>0.529</v>
+        <v>0.54</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J9" t="n">
         <v>79.09999999999999</v>
@@ -1965,16 +2032,16 @@
         <v>13.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O9" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P9" t="n">
         <v>22.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R9" t="n">
         <v>10.8</v>
@@ -1989,7 +2056,7 @@
         <v>20.2</v>
       </c>
       <c r="V9" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="W9" t="n">
         <v>6.5</v>
@@ -2004,31 +2071,31 @@
         <v>21.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB9" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
         <v>14</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
         <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
@@ -2061,10 +2128,10 @@
         <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2076,7 +2143,7 @@
         <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2085,7 +2152,7 @@
         <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2213,7 +2280,7 @@
         <v>2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
         <v>15</v>
@@ -2225,7 +2292,7 @@
         <v>15</v>
       </c>
       <c r="AN10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
         <v>8</v>
@@ -2246,10 +2313,10 @@
         <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
         <v>7</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
         <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.604</v>
+        <v>0.596</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,7 +2384,7 @@
         <v>35.5</v>
       </c>
       <c r="J11" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0.445</v>
@@ -2326,7 +2393,7 @@
         <v>7.6</v>
       </c>
       <c r="M11" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N11" t="n">
         <v>0.372</v>
@@ -2335,13 +2402,13 @@
         <v>19.8</v>
       </c>
       <c r="P11" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S11" t="n">
         <v>32.1</v>
@@ -2353,16 +2420,16 @@
         <v>20.3</v>
       </c>
       <c r="V11" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X11" t="n">
         <v>3.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z11" t="n">
         <v>19</v>
@@ -2374,10 +2441,10 @@
         <v>98.40000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2386,13 +2453,13 @@
         <v>10</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
         <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ11" t="n">
         <v>16</v>
@@ -2401,13 +2468,13 @@
         <v>25</v>
       </c>
       <c r="AL11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM11" t="n">
         <v>8</v>
       </c>
-      <c r="AM11" t="n">
-        <v>6</v>
-      </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
         <v>10</v>
@@ -2419,13 +2486,13 @@
         <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
         <v>21</v>
@@ -2446,7 +2513,7 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>0.389</v>
+        <v>0.396</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
@@ -2502,37 +2569,37 @@
         <v>85.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M12" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N12" t="n">
         <v>0.371</v>
       </c>
       <c r="O12" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="P12" t="n">
         <v>23.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U12" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V12" t="n">
         <v>15</v>
@@ -2541,25 +2608,25 @@
         <v>6.9</v>
       </c>
       <c r="X12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="n">
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.8</v>
+        <v>104.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2568,10 +2635,10 @@
         <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI12" t="n">
         <v>3</v>
@@ -2583,19 +2650,19 @@
         <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>13</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
         <v>4</v>
@@ -2610,28 +2677,28 @@
         <v>3</v>
       </c>
       <c r="AU12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC12" t="n">
         <v>21</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -2663,64 +2730,64 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
         <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>0.245</v>
+        <v>0.231</v>
       </c>
       <c r="H13" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>35.7</v>
+        <v>35.4</v>
       </c>
       <c r="J13" t="n">
-        <v>82.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L13" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="M13" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O13" t="n">
         <v>17</v>
       </c>
       <c r="P13" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R13" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S13" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T13" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U13" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="V13" t="n">
         <v>14.8</v>
       </c>
       <c r="W13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
         <v>6.1</v>
@@ -2735,28 +2802,28 @@
         <v>19.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>-7.6</v>
+        <v>-7.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI13" t="n">
         <v>27</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>25</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2765,13 +2832,13 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AM13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
@@ -2780,7 +2847,7 @@
         <v>26</v>
       </c>
       <c r="AQ13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR13" t="n">
         <v>11</v>
@@ -2789,31 +2856,31 @@
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>25</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -2848,85 +2915,85 @@
         <v>51</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>0.804</v>
+        <v>0.824</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="J14" t="n">
-        <v>84.8</v>
+        <v>84.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.479</v>
       </c>
       <c r="L14" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.366</v>
+        <v>0.372</v>
       </c>
       <c r="O14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="P14" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R14" t="n">
         <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>44.1</v>
+        <v>44.3</v>
       </c>
       <c r="U14" t="n">
         <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W14" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y14" t="n">
         <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.9</v>
+        <v>108.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>1</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2962,13 +3029,13 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2977,28 +3044,28 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>0.288</v>
+        <v>0.294</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
@@ -3045,31 +3112,31 @@
         <v>34.6</v>
       </c>
       <c r="J15" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>0.449</v>
       </c>
       <c r="L15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
         <v>13.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="O15" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P15" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R15" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S15" t="n">
         <v>28.8</v>
@@ -3078,16 +3145,16 @@
         <v>39</v>
       </c>
       <c r="U15" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="W15" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y15" t="n">
         <v>5.1</v>
@@ -3096,16 +3163,16 @@
         <v>21.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.2</v>
+        <v>93.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,10 +3184,10 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ15" t="n">
         <v>28</v>
@@ -3135,40 +3202,40 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS15" t="n">
         <v>25</v>
       </c>
       <c r="AT15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ15" t="n">
         <v>20</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
         <v>18</v>
@@ -3308,7 +3375,7 @@
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3317,22 +3384,22 @@
         <v>11</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
         <v>28</v>
       </c>
       <c r="AR16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS16" t="n">
         <v>22</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>23</v>
       </c>
       <c r="AT16" t="n">
         <v>25</v>
@@ -3347,13 +3414,13 @@
         <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
         <v>6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
         <v>26</v>
@@ -3362,7 +3429,7 @@
         <v>24</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -3394,82 +3461,82 @@
         <v>54</v>
       </c>
       <c r="E17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.481</v>
+        <v>0.463</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J17" t="n">
         <v>81.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M17" t="n">
         <v>16.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.358</v>
+        <v>0.355</v>
       </c>
       <c r="O17" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="P17" t="n">
-        <v>26</v>
+        <v>25.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.783</v>
+        <v>0.785</v>
       </c>
       <c r="R17" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="T17" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y17" t="n">
         <v>4.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.5</v>
+        <v>99</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3484,13 +3551,13 @@
         <v>17</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ17" t="n">
         <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3499,28 +3566,28 @@
         <v>22</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>7</v>
       </c>
       <c r="AP17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>8</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>9</v>
       </c>
       <c r="AR17" t="n">
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
@@ -3532,19 +3599,19 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3669,22 +3736,22 @@
         <v>13</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO18" t="n">
         <v>18</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>17</v>
       </c>
       <c r="AP18" t="n">
         <v>17</v>
@@ -3702,7 +3769,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
@@ -3720,7 +3787,7 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3848,10 +3915,10 @@
         <v>7</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
         <v>27</v>
@@ -3860,7 +3927,7 @@
         <v>7</v>
       </c>
       <c r="AM19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN19" t="n">
         <v>8</v>
@@ -3869,10 +3936,10 @@
         <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
         <v>13</v>
@@ -3887,10 +3954,10 @@
         <v>28</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -3937,64 +4004,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E20" t="n">
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6</v>
+        <v>0.612</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="J20" t="n">
-        <v>76.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L20" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.383</v>
+        <v>0.385</v>
       </c>
       <c r="O20" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S20" t="n">
         <v>28.8</v>
       </c>
       <c r="T20" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="U20" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V20" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W20" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
         <v>4.3</v>
@@ -4006,31 +4073,31 @@
         <v>20.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.3</v>
+        <v>95.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG20" t="n">
         <v>8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>10</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ20" t="n">
         <v>29</v>
@@ -4039,16 +4106,16 @@
         <v>16</v>
       </c>
       <c r="AL20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM20" t="n">
         <v>9</v>
       </c>
-      <c r="AM20" t="n">
-        <v>10</v>
-      </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
@@ -4072,13 +4139,13 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ20" t="n">
         <v>14</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>0.404</v>
+        <v>0.412</v>
       </c>
       <c r="H21" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J21" t="n">
-        <v>86.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0.443</v>
       </c>
       <c r="L21" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="M21" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.358</v>
+        <v>0.361</v>
       </c>
       <c r="O21" t="n">
         <v>18</v>
@@ -4161,19 +4228,19 @@
         <v>0.799</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T21" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U21" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V21" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
@@ -4191,13 +4258,13 @@
         <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.1</v>
+        <v>104.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4209,13 +4276,13 @@
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
@@ -4245,16 +4312,16 @@
         <v>9</v>
       </c>
       <c r="AT21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU21" t="n">
         <v>9</v>
       </c>
-      <c r="AU21" t="n">
-        <v>8</v>
-      </c>
       <c r="AV21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,13 +4330,13 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -4301,61 +4368,61 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" t="n">
         <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
-        <v>0.245</v>
+        <v>0.25</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J22" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.449</v>
+        <v>0.451</v>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M22" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="N22" t="n">
-        <v>0.37</v>
+        <v>0.373</v>
       </c>
       <c r="O22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R22" t="n">
         <v>12.1</v>
       </c>
       <c r="S22" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T22" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U22" t="n">
         <v>20.3</v>
       </c>
       <c r="V22" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W22" t="n">
         <v>6.8</v>
@@ -4367,19 +4434,19 @@
         <v>5.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA22" t="n">
         <v>21</v>
       </c>
       <c r="AB22" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.8</v>
+        <v>-5.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4394,13 +4461,13 @@
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,28 +4476,28 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>13</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS22" t="n">
         <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -4483,85 +4550,85 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E23" t="n">
         <v>38</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>0.745</v>
+        <v>0.76</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.1</v>
+        <v>36.4</v>
       </c>
       <c r="J23" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.463</v>
       </c>
       <c r="L23" t="n">
         <v>10.4</v>
       </c>
       <c r="M23" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.396</v>
+        <v>0.399</v>
       </c>
       <c r="O23" t="n">
         <v>19.6</v>
       </c>
       <c r="P23" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="R23" t="n">
         <v>10.1</v>
       </c>
       <c r="S23" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T23" t="n">
         <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="W23" t="n">
         <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y23" t="n">
         <v>3.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.2</v>
+        <v>102.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4618,25 +4685,25 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
         <v>3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F24" t="n">
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>0.529</v>
+        <v>0.52</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4683,43 +4750,43 @@
         <v>36.7</v>
       </c>
       <c r="J24" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M24" t="n">
         <v>13.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.322</v>
+        <v>0.324</v>
       </c>
       <c r="O24" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P24" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="R24" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S24" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T24" t="n">
-        <v>42.5</v>
+        <v>42.9</v>
       </c>
       <c r="U24" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V24" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W24" t="n">
         <v>8.1</v>
@@ -4728,7 +4795,7 @@
         <v>5.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
         <v>20.1</v>
@@ -4737,31 +4804,31 @@
         <v>21</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>14</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>15</v>
       </c>
       <c r="AK24" t="n">
         <v>12</v>
@@ -4791,34 +4858,34 @@
         <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU24" t="n">
         <v>16</v>
       </c>
       <c r="AV24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW24" t="n">
         <v>5</v>
       </c>
       <c r="AX24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB24" t="n">
         <v>23</v>
       </c>
       <c r="BC24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" t="n">
         <v>28</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>0.549</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K25" t="n">
         <v>0.494</v>
@@ -4874,16 +4941,16 @@
         <v>6.3</v>
       </c>
       <c r="M25" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O25" t="n">
         <v>20.9</v>
       </c>
       <c r="P25" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="Q25" t="n">
         <v>0.761</v>
@@ -4892,7 +4959,7 @@
         <v>9.9</v>
       </c>
       <c r="S25" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T25" t="n">
         <v>41.6</v>
@@ -4901,16 +4968,16 @@
         <v>21.9</v>
       </c>
       <c r="V25" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="W25" t="n">
         <v>6.4</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z25" t="n">
         <v>20.4</v>
@@ -4919,13 +4986,13 @@
         <v>22.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.4</v>
+        <v>104.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4934,7 +5001,7 @@
         <v>12</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>22</v>
@@ -4955,7 +5022,7 @@
         <v>20</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
@@ -4964,13 +5031,13 @@
         <v>4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT25" t="n">
         <v>14</v>
@@ -4988,7 +5055,7 @@
         <v>12</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
         <v>12</v>
@@ -5000,7 +5067,7 @@
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -5032,58 +5099,58 @@
         <v>50</v>
       </c>
       <c r="E26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.461</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N26" t="n">
         <v>0.382</v>
       </c>
       <c r="O26" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R26" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="T26" t="n">
         <v>40.9</v>
       </c>
       <c r="U26" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V26" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>6.9</v>
@@ -5092,22 +5159,22 @@
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5122,13 +5189,13 @@
         <v>12</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5137,16 +5204,16 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
         <v>16</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,31 +5222,31 @@
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX26" t="n">
         <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E27" t="n">
         <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G27" t="n">
-        <v>0.204</v>
+        <v>0.208</v>
       </c>
       <c r="H27" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I27" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J27" t="n">
-        <v>81</v>
+        <v>81.3</v>
       </c>
       <c r="K27" t="n">
         <v>0.445</v>
       </c>
       <c r="L27" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M27" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O27" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="P27" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.803</v>
+        <v>0.804</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S27" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="T27" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="U27" t="n">
         <v>19.9</v>
       </c>
       <c r="V27" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W27" t="n">
         <v>6.8</v>
@@ -5274,22 +5341,22 @@
         <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z27" t="n">
         <v>23.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC27" t="n">
         <v>-9.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>29</v>
@@ -5301,10 +5368,10 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>12</v>
@@ -5319,7 +5386,7 @@
         <v>14</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
         <v>6</v>
@@ -5331,7 +5398,7 @@
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS27" t="n">
         <v>28</v>
@@ -5343,7 +5410,7 @@
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW27" t="n">
         <v>24</v>
@@ -5352,7 +5419,7 @@
         <v>26</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ27" t="n">
         <v>29</v>
@@ -5361,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
         <v>35</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,37 +5478,37 @@
         <v>37</v>
       </c>
       <c r="J28" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L28" t="n">
         <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N28" t="n">
         <v>0.392</v>
       </c>
       <c r="O28" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P28" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R28" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T28" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="U28" t="n">
         <v>22</v>
@@ -5456,25 +5523,25 @@
         <v>4.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.8</v>
+        <v>98</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF28" t="n">
         <v>5</v>
@@ -5489,16 +5556,16 @@
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AN28" t="n">
         <v>2</v>
@@ -5513,10 +5580,10 @@
         <v>15</v>
       </c>
       <c r="AR28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>22</v>
@@ -5534,7 +5601,7 @@
         <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
         <v>34</v>
       </c>
       <c r="G29" t="n">
-        <v>0.382</v>
+        <v>0.37</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5608,13 +5675,13 @@
         <v>0.374</v>
       </c>
       <c r="O29" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.828</v>
+        <v>0.827</v>
       </c>
       <c r="R29" t="n">
         <v>8.699999999999999</v>
@@ -5626,7 +5693,7 @@
         <v>39</v>
       </c>
       <c r="U29" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="V29" t="n">
         <v>13.2</v>
@@ -5644,19 +5711,19 @@
         <v>19.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>96.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="AD29" t="n">
         <v>1</v>
       </c>
       <c r="AE29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
@@ -5668,16 +5735,16 @@
         <v>21</v>
       </c>
       <c r="AI29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>24</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>23</v>
       </c>
       <c r="AK29" t="n">
         <v>11</v>
       </c>
       <c r="AL29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM29" t="n">
         <v>21</v>
@@ -5686,25 +5753,25 @@
         <v>10</v>
       </c>
       <c r="AO29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS29" t="n">
         <v>14</v>
       </c>
       <c r="AT29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
         <v>8</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J30" t="n">
-        <v>79.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.478</v>
+        <v>0.476</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
@@ -5787,25 +5854,25 @@
         <v>14.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="O30" t="n">
         <v>21.6</v>
       </c>
       <c r="P30" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.766</v>
+        <v>0.768</v>
       </c>
       <c r="R30" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S30" t="n">
         <v>29.3</v>
       </c>
       <c r="T30" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U30" t="n">
         <v>24.6</v>
@@ -5826,25 +5893,25 @@
         <v>22.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>102.6</v>
+        <v>102.4</v>
       </c>
       <c r="AC30" t="n">
         <v>2.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
         <v>15</v>
@@ -5853,7 +5920,7 @@
         <v>7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
         <v>4</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,40 +5941,40 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
         <v>16</v>
       </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA30" t="n">
         <v>1</v>
       </c>
       <c r="BB30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC30" t="n">
         <v>9</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" t="n">
         <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G31" t="n">
-        <v>0.208</v>
+        <v>0.212</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5963,19 +6030,19 @@
         <v>0.444</v>
       </c>
       <c r="L31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M31" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.328</v>
+        <v>0.324</v>
       </c>
       <c r="O31" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P31" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q31" t="n">
         <v>0.762</v>
@@ -5984,13 +6051,13 @@
         <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T31" t="n">
         <v>39.7</v>
       </c>
       <c r="U31" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V31" t="n">
         <v>13.8</v>
@@ -6002,7 +6069,7 @@
         <v>3.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z31" t="n">
         <v>20.5</v>
@@ -6011,13 +6078,13 @@
         <v>19.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC31" t="n">
         <v>-8</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6032,7 +6099,7 @@
         <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
         <v>10</v>
@@ -6059,7 +6126,7 @@
         <v>18</v>
       </c>
       <c r="AR31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS31" t="n">
         <v>29</v>
@@ -6074,13 +6141,13 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>27</v>
       </c>
       <c r="AY31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-11-2008-09</t>
+          <t>2009-02-11</t>
         </is>
       </c>
     </row>
